--- a/QCM3_5_PHY.xlsx
+++ b/QCM3_5_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3152648-EC5D-4F2A-83CA-751D30BB7420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDD773C-859C-4286-AFE7-9A60351B66D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>$E = 9\text{ V}$</t>
   </si>
   <si>
-    <t>$C = 10\text{ nF}$</t>
-  </si>
-  <si>
     <t>$L = 10\text{ mH}$</t>
   </si>
   <si>
@@ -120,30 +117,12 @@
     <t>$C = 1\text{ mF}$</t>
   </si>
   <si>
-    <t>$C = 1\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>$C = 10\text{ \mu F}$</t>
-  </si>
-  <si>
     <t>$E = 50\text{ mJ}$</t>
   </si>
   <si>
-    <t>$E = 50\text{ \mu J}$</t>
-  </si>
-  <si>
     <t>$E = 5\text{ mJ}$</t>
   </si>
   <si>
-    <t>$E = 5\text{ \mu J}$</t>
-  </si>
-  <si>
-    <t>$i(t) = q \cdot dt$</t>
-  </si>
-  <si>
-    <t>$i(t) = -q \cdot dt$</t>
-  </si>
-  <si>
     <t>maximale</t>
   </si>
   <si>
@@ -153,24 +132,9 @@
     <t>nulle</t>
   </si>
   <si>
-    <t>$T = 6,28\text{ \mu s}$</t>
-  </si>
-  <si>
-    <t>$T = 62,8\text{ \mu s}$</t>
-  </si>
-  <si>
-    <t>$T = 628\text{ \mu s}$</t>
-  </si>
-  <si>
-    <t>$T = 6280\text{ \mu s}$</t>
-  </si>
-  <si>
     <t>$\varphi = \frac{\pi}{2}$</t>
   </si>
   <si>
-    <t>$\varphi = -\frac{\pi}{6}$</t>
-  </si>
-  <si>
     <t>$\varphi = \pi$</t>
   </si>
   <si>
@@ -225,30 +189,12 @@
     <t>$q(t) = 5\cdot 10^{-6}(1 - e^{-10^2 t})$</t>
   </si>
   <si>
-    <t>$q(t) = 6\cdot 10^{-6}(1 - e^{-10^4 t})$</t>
-  </si>
-  <si>
     <t>$q(t) = 5\cdot 10^{-6} e^{-10^4 t}$</t>
   </si>
   <si>
     <t>$q(t) = 5\cdot 10^{-6}(1 - e^{-10^4 t})$</t>
   </si>
   <si>
-    <t>$R_2$: courbe (2), $R_3$: courbe (3), $R_1$: courbe (1)</t>
-  </si>
-  <si>
-    <t>$R_2$: courbe (3), $R_3$: courbe (1), $R_1$: courbe (2)</t>
-  </si>
-  <si>
-    <t>$R_2$: courbe (1), $R_3$: courbe (2), $R_1$: courbe (3)</t>
-  </si>
-  <si>
-    <t>$R_2$: courbe (3), $R_3$: courbe (2), $R_1$: courbe (1)</t>
-  </si>
-  <si>
-    <t>$R_2$: courbe (1), $R_3$: courbe (3), $R_1$: courbe (2)</t>
-  </si>
-  <si>
     <t>$T = 12,6\text{ ms}$</t>
   </si>
   <si>
@@ -270,18 +216,6 @@
     <t>$L = 0,1\text{ mH}$</t>
   </si>
   <si>
-    <t>$\Delta E = -9,12\text{ \mu J}$</t>
-  </si>
-  <si>
-    <t>$\Delta E = 3,12\text{ \mu J}$</t>
-  </si>
-  <si>
-    <t>$\Delta E = 9,12\text{ \mu J}$</t>
-  </si>
-  <si>
-    <t>$\Delta E = -3,12\text{ \mu J}$</t>
-  </si>
-  <si>
     <t>$R = 0$</t>
   </si>
   <si>
@@ -324,9 +258,6 @@
     <t>constante</t>
   </si>
   <si>
-    <t>$C = 2\text{ \mu F}$</t>
-  </si>
-  <si>
     <t>$C = 1\text{ nF}$</t>
   </si>
   <si>
@@ -345,9 +276,6 @@
     <t>Le condensateur a une capacité :</t>
   </si>
   <si>
-    <t>L'énergie totale du circuit :</t>
-  </si>
-  <si>
     <t>L'intensité $i(t)$ a pour expression :</t>
   </si>
   <si>
@@ -399,30 +327,6 @@
     <t>La tension $U_0$ a pour valeur :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuit RLC série : &lt;/b&gt;&lt;/center&gt;
-Soit le schéma du montage ci-contre, comprenant une bobine d'inductance $L$ et un condensateur de capacité $C$. L'interrupteur K est ouvert ; la tension aux bornes du condensateur $U_{AB} = 10\text{ V}$. On considère que la résistance de la bobine et des fils de connexion est nulle. A l'instant $t = 0$, on ferme l'interrupteur K. A l'aide d'un système informatique, des enregistrements ont été effectués et ont donné les expressions suivantes : $u_{AB}(t) = 10\cos(10^3 t)$ avec $u_{AB}(t)$ en volt, $t$ en seconde ; $i(t) = 10^{-2}\sin(10^3 t)$ avec $i(t)$ en ampère, $t$ en seconde.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuit LC : &lt;/b&gt;&lt;/center&gt;
-Le circuit ci-après est composé d'une source de tension continue $E$, d'une bobine d'inductance $L$, d'un condensateur de capacité $C$, d'un conducteur ohmique $R$ et d'un interrupteur K. Initialement le condensateur et la bobine ne possèdent pas d'énergie. Dans un premier temps, on positionne l'interrupteur K en position 1. Lorsque la tension $u(t)$ atteint la valeur $E$, on bascule l'interrupteur en position 2 ; cet instant est choisi comme origine des temps. Il s'établit alors dans le circuit LC un courant sinusoïdal et l'évolution de la charge du condensateur au cours du temps s'écrit : $q(t) = Q \cos(\frac{2\pi}{T}t + \varphi)$ ; $E = 10,0\text{ V} ; L = 0,10\text{ H} ; C = 0,10\text{ \mu F}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuits RC et RLC : &lt;/b&gt;&lt;/center&gt;
-On considère le montage comportant un générateur idéal de tension $E$ ; Un condensateur $C = 1\text{ \mu F}$ ; Un conducteur ohmique de résistance $R_0$ et un autre de résistance $R$ réglable ; Une bobine d'inductance $L$ et de résistance négligeable. A l'instant $t_0 = 0$, on place l'interrupteur K en position (1). La courbe obtenue représente la variation de la charge $q$ du condensateur en fonction du temps.</t>
-  </si>
-  <si>
-    <t>Lorsque le condensateur est totalement chargé, on bascule l'interrupteur en position (2) à un instant pris comme nouvelle origine de temps $t_0 = 0$. Les courbes (1), (2) et (3) représentent la tension $U_C(t)$ pour trois valeurs de résistance : $R_1 = 10\ \Omega$, $R_2 = 2\text{ k}\Omega$ et $R_3 = 20\text{ k}\Omega$.
-Attribuer chaque courbe à la résistance correspondante :</t>
-  </si>
-  <si>
-    <t>On considère le point S de la courbe (2) de coordonnées : $t_S = 12,6\text{ ms}$ ; $U_{CS} = 2,6\text{ V}$.
-La valeur de la pseudo-période $T$ :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuits RC et LC : &lt;/b&gt;&lt;/center&gt;
-Soit le circuit ci-contre comprenant un générateur idéal de tension $E = 10\text{ V}$, deux interrupteurs $K_1$ et $K_2$, une bobine inductive $L$ (de résistance interne nulle), un conducteur ohmique $R = 1\text{ k}\Omega$ et un condensateur de capacité $C = 30\text{ nF}$. Le condensateur étant chargé, on ouvre l'interrupteur $K_1$ et on ferme l'interrupteur $K_2$. On prendra $\pi^2 = 10$, la période des oscillations dans le circuit mesurée est $T_p = 6 \cdot 10^{-5}\text{ s}$.</t>
-  </si>
-  <si>
     <t>Dans le circuit de la question précédente, l'énergie électromagnétique E du circuit LC vaut :</t>
   </si>
   <si>
@@ -438,18 +342,6 @@
     <t>$E=150.10^{-7} J$</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Circuit RLC : &lt;/b&gt;&lt;/center&gt;
-Un circuit électrique série comporte une bobine $(L, r = 0)$, un conducteur ohmique de résistance $R$ et un condensateur de capacité $C = 2 \cdot 10^{-6}\text{ F}$. On ferme le circuit à $t=0$, le document ci-contre représente les variations de la tension $u_C(t)$ aux bornes du condensateur.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Etude d'un circuit LC : &lt;/b&gt;&lt;/center&gt;
-On utilise dans cette étude une bobine d'inductance $L = 0,6\text{ H}$ et de résistance négligeable. Après avoir chargé totalement un condensateur de capacité $C$ sous une tension constante $U_0$, on le branche aux bornes de la bobine. La tension aux bornes du condensateur peut s'écrire sous la forme : $u_C(t) = U_0 \cos(2\pi f_0 t + \varphi)$ où $f_0$ est la fréquence propre du circuit.</t>
-  </si>
-  <si>
-    <t>La courbe de la figure ci-contre représente la variation de l'énergie magnétique $E_m$ emmagasinée dans la bobine en fonction du carré de la tension $u_C$ aux bornes du condensateur : $E_m = f(u_C^2)$.
-La capacité $C$ du condensateur a pour valeur :</t>
-  </si>
-  <si>
     <t>PHY_QCM3_5_Q1.png</t>
   </si>
   <si>
@@ -475,10 +367,6 @@
   </si>
   <si>
     <t>$T = 6,3\text{ ms}$</t>
-  </si>
-  <si>
-    <t>(2) pseudopériodique 
-(3) : apériodique</t>
   </si>
   <si>
     <t>(2) : périodique 
@@ -504,6 +392,123 @@
   </si>
   <si>
     <t>$U_0 = 20\text{ V}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuit RLC série : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Soit le schéma du montage ci-contre, comprenant une bobine d'inductance $L$ et un condensateur de capacité $C$. L'interrupteur K est ouvert ; la tension aux bornes du condensateur $U_{AB} = 10\text{ V}$. On considère que la résistance de la bobine et des fils de connexion est nulle. A l'instant $t = 0$, on ferme l'interrupteur K. A l'aide d'un système informatique, des enregistrements ont été effectués et ont donné les expressions suivantes : $u_{AB}(t) = 10\cos(10^3 t)$ avec $u_{AB}(t)$ en volt, $t$ en seconde ; $i(t) = 10^{-2}\sin(10^3 t)$ avec $i(t)$ en ampère, $t$ en seconde.</t>
+  </si>
+  <si>
+    <t>$C = 10\text{ mF}$</t>
+  </si>
+  <si>
+    <t>$C = 1\mu F$</t>
+  </si>
+  <si>
+    <t>$C = 10 \mu F$</t>
+  </si>
+  <si>
+    <t>L'énergie emmagasinée dans le circuit a pour valeur :</t>
+  </si>
+  <si>
+    <t>$E = 50 \mu J$</t>
+  </si>
+  <si>
+    <t>$E = 5 \mu J$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuit LC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Le circuit ci-après est composé d'une source de tension continue $E$, d'une bobine d'inductance $L$, d'un condensateur de capacité $C$, d'un conducteur ohmique $R$ et d'un interrupteur K. Initialement le condensateur et la bobine ne possèdent pas d'énergie. Dans un premier temps, on positionne l'interrupteur K en position 1. Lorsque la tension $u(t)$ atteint la valeur $E$, on bascule l'interrupteur en position 2 ; cet instant est choisi comme origine des temps. Il s'établit alors dans le circuit LC un courant sinusoïdal et l'évolution de la charge du condensateur au cours du temps s'écrit : $q(t) = Q \cos(\frac{2\pi}{T}t + \varphi)$ ; $E = 10,0\text{ V} ; L = 0,10\text{ H} ; C = 0,10 \mu F$.</t>
+  </si>
+  <si>
+    <t>$i(t) = q \cdot \delta t$</t>
+  </si>
+  <si>
+    <t>$i(t) = -q \cdot \delta t$</t>
+  </si>
+  <si>
+    <t>$T = 6,28\mu s$</t>
+  </si>
+  <si>
+    <t>$T = 62,8\mu s$</t>
+  </si>
+  <si>
+    <t>$T = 628 \mu s$</t>
+  </si>
+  <si>
+    <t>$T = 6280 \mu s$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuits RC et RLC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On considère le montage de la figure 1 comportant :
+&lt;br&gt; * un générateur idéal de tension de force électromotrice $E$ ; 
+&lt;br&gt; * Un condensateur $C = 1 \mu F$ ; 
+&lt;br&gt; * Un conducteur ohmique de résistance $R_0$ et un autre de résistance $R$ réglable ; 
+&lt;br&gt; * Une bobine d'inductance $L$ et de résistance négligeable. 
+&lt;br&gt; * un interrupteur K à double position.
+&lt;br&gt;A l'instant $t_0 = 0$, on place l'interrupteur K en position (1). Un système d'aquisition convenable permet d'obtenir la courbe (Figure 2) représentant la variation de la charge $q$ du condensateur en fonction du temps.</t>
+  </si>
+  <si>
+    <t>$q(t) = 6\cdot 10^{-6}(1 - e^{-10^5 t})$</t>
+  </si>
+  <si>
+    <t>Lorsque le condensateur est totalement chargé, on bascule l'interrupteur en position (2) à un instant pris comme nouvelle origine de temps $t_0 = 0$. Les courbes (1), (2) et (3) représentent la tension $U_C(t)$ pour trois valeurs de résistance : $R_1 = 100\ \Omega$, $R_2 = 2\text{ k}\Omega$ et $R_3 = 20\text{ k}\Omega$.
+&lt;br&gt;Attribuer chaque courbe à la résistance correspondante :</t>
+  </si>
+  <si>
+    <t>$R_1$: courbe (1), &lt;br&gt;$R_2$: courbe (2), &lt;br&gt;$R_3$: courbe (3)</t>
+  </si>
+  <si>
+    <t>$R_1$: courbe (2), &lt;br&gt;$R_2$: courbe (3), &lt;br&gt;$R_3$: courbe (1)</t>
+  </si>
+  <si>
+    <t>$R_1$: courbe (3), &lt;br&gt;$R_2$: courbe (1), &lt;br&gt;$R_3$: courbe (2)</t>
+  </si>
+  <si>
+    <t>$R_1$: courbe (1), &lt;br&gt;$R_2$: courbe (3), &lt;br&gt;$R_3$: courbe (2)</t>
+  </si>
+  <si>
+    <t>$R_1$: courbe (2), &lt;br&gt;$R_2$: courbe (1), &lt;br&gt;$R_3$: courbe (3)</t>
+  </si>
+  <si>
+    <t>On considère le point S de la courbe (2) de coordonnées : $t_S = 12,6\text{ ms}$ ; $U_{CS} = 2,6\text{ V}$.
+&lt;br&gt;La valeur de la pseudo-période $T$ des oscillations :</t>
+  </si>
+  <si>
+    <t>$\Delta E = -9,12\mu J$</t>
+  </si>
+  <si>
+    <t>$\Delta E = 3,12 \mu J$</t>
+  </si>
+  <si>
+    <t>$\Delta E = 9,12\mu J$</t>
+  </si>
+  <si>
+    <t>$\Delta E = -3,12\mu J$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuits RC et LC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Soit le circuit ci-contre comprenant un générateur idéal de tension $E = 10\text{ V}$, deux interrupteurs $K_1$ et $K_2$, une bobine inductive $L$ (de résistance interne nulle), un conducteur ohmique $R = 1\text{ k}\Omega$ et un condensateur de capacité $C = 30\text{ nF}$. Le condensateur étant chargé, on ouvre l'interrupteur $K_1$ et on ferme l'interrupteur $K_2$. On prendra $\pi^2 = 10$, la période des oscillations dans le circuit mesurée est $T_p = 6 \cdot 10^{-5}\text{ s}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Circuit RLC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+Un circuit électrique série comporte une bobine $(L, r = 0)$, un conducteur ohmique de résistance $R$ et un condensateur de capacité $C = 2 \cdot 10^{-6}\text{ F}$. On ferme le circuit à $t=0$, le document ci-contre représente les variations de la tension $u_C(t)$ aux bornes du condensateur.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Etude d'un circuit LC : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On utilise dans cette étude une bobine d'inductance $L = 0,6\text{ H}$ et de résistance négligeable. Après avoir chargé totalement un condensateur de capacité $C$ sous une tension constante $U_0$, on le branche aux bornes de la bobine. La tension aux bornes du condensateur peut s'écrire sous la forme : $u_C(t) = U_0 \cos(2\pi f_0 t + \varphi)$ où $f_0$ est la fréquence propre du circuit.</t>
+  </si>
+  <si>
+    <t>La courbe de la figure ci-contre représente la variation de l'énergie magnétique $E_m$ emmagasinée dans la bobine en fonction du carré de la tension $u_C$ aux bornes du condensateur : $E_m = f(u_C^2)$.
+&lt;br&gt;La capacité $C$ du condensateur a pour valeur :</t>
+  </si>
+  <si>
+    <t>$C = 1 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 2 \mu F$</t>
   </si>
 </sst>
 </file>
@@ -1028,58 +1033,58 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
@@ -1087,111 +1092,111 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="7" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" ht="204" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1199,26 +1204,26 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="7" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1226,77 +1231,77 @@
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="204" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="7" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>12</v>
@@ -1305,7 +1310,7 @@
         <v>14</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1313,59 +1318,59 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1373,26 +1378,26 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1400,327 +1405,327 @@
     <row r="15" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="J15" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="G16" s="7" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="9" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="7" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="J21" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="9" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="J23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="9" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
